--- a/astro-site/public/dl/kit-tareas-chef-privado/BONUS-02-calendario-anual-demanda.xlsx
+++ b/astro-site/public/dl/kit-tareas-chef-privado/BONUS-02-calendario-anual-demanda.xlsx
@@ -1,16 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Calendario Anual" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Calendario Anual" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Calendario Anual'!$4:$4</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -136,47 +138,47 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="15">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="2" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="3" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="4" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="5" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="10" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -536,15 +538,16 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:B11"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="3"/>
-    <col customWidth="1" max="2" min="2" width="80"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="80" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -552,6 +555,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -580,9 +584,7 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="B8" t="inlineStr"/>
-    </row>
+    <row r="8"/>
     <row r="9">
       <c r="B9" s="2" t="inlineStr">
         <is>
@@ -604,8 +606,25 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
+    <row r="13">
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-tareas-chef-privado · info@aichef.pro</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -614,17 +633,17 @@
   <sheetPr>
     <tabColor rgb="00E91E63"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="16"/>
-    <col customWidth="1" max="2" min="2" width="50"/>
-    <col customWidth="1" max="3" min="3" width="20"/>
-    <col customWidth="1" max="4" min="4" width="14"/>
-    <col customWidth="1" max="5" min="5" width="14"/>
-    <col customWidth="1" max="6" min="6" width="20"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -641,6 +660,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -937,6 +957,7 @@
       <c r="E15" s="10" t="n"/>
       <c r="F15" s="11" t="n"/>
     </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" s="14" t="inlineStr">
         <is>
@@ -951,10 +972,19 @@
     <mergeCell ref="A17:F17"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" error="Usa ✓, ✗ o —" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="E5 E6 E7 E8 E9 E10 E11 E12 E13 E14 E15" type="list">
+    <dataValidation sqref="E5 E6 E7 E8 E9 E10 E11 E12 E13 E14 E15" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Usa ✓, ✗ o —" type="list">
       <formula1>"✓,✗,—"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>